--- a/data/CReDEs/jy/jy_zkjc.xlsx
+++ b/data/CReDEs/jy/jy_zkjc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\九院-标准化\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\九院-标准化\CRedes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766EDB86-38B2-4EAA-B02D-BBE2E816021C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDFF667-0BFF-4A25-9B96-2E81FA9D08C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" xr2:uid="{485A1444-4D81-47A9-B478-74CC4ACD75AE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
   <si>
     <t>标签名称</t>
   </si>
@@ -166,6 +166,10 @@
   </si>
   <si>
     <t>1=左侧， 2=右侧， 3=双侧， 4=不详</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -647,7 +651,9 @@
       <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -665,7 +671,9 @@
       <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -703,7 +711,9 @@
       <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -741,7 +751,9 @@
       <c r="E10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -759,7 +771,9 @@
       <c r="E11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -769,5 +783,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>